--- a/files/R01-R69全节点业务验收测试包/V00_R01-R69覆盖验证/V00_V00-REQ-MATRIX-001_TEST-V00-002_166项资料要求覆盖明细.xlsx
+++ b/files/R01-R69全节点业务验收测试包/V00_R01-R69覆盖验证/V00_V00-REQ-MATRIX-001_TEST-V00-002_166项资料要求覆盖明细.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="166项要求" sheetId="1" r:id="Rb1c2bd13220348fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="166项要求" sheetId="1" r:id="Rd77b1f9dd72d42e9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -59,8 +59,13 @@
         <x:fgColor rgb="FFFCE8E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3F1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left/>
@@ -90,11 +95,63 @@
       <x:right/>
       <x:bottom/>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -186,6 +243,70 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -216,6 +337,38 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="06a14020-3476-47d7-8fea-782eefee43e3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6fb01a28035840e1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -418,7 +571,7 @@
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" hidden="0" customHeight="1">
@@ -479,7 +632,7 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F5" s="34" t="str">
-        <x:v>B00-QUAL-001#REQ-01-01</x:v>
+        <x:v>B00-QUAL-001#REQ-01-01 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -499,7 +652,7 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F6" s="37" t="str">
-        <x:v>B00-QUAL-001#REQ-01-02</x:v>
+        <x:v>B00-QUAL-001#REQ-01-02 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -519,7 +672,7 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F7" s="37" t="str">
-        <x:v>B00-QUAL-001#REQ-01-03</x:v>
+        <x:v>B00-QUAL-001#REQ-01-03 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -539,7 +692,7 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F8" s="37" t="str">
-        <x:v>B00-QUAL-001#REQ-02-01</x:v>
+        <x:v>B00-QUAL-001#REQ-02-01 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -559,7 +712,7 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F9" s="37" t="str">
-        <x:v>B00-QUAL-001#REQ-02-02</x:v>
+        <x:v>B00-QUAL-001#REQ-02-02 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -579,7 +732,7 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F10" s="37" t="str">
-        <x:v>B00-QUAL-001#REQ-02-03</x:v>
+        <x:v>B00-QUAL-001#REQ-02-03 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -599,7 +752,7 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F11" s="37" t="str">
-        <x:v>B00-QUAL-001#REQ-03-01</x:v>
+        <x:v>B00-QUAL-001#REQ-03-01 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -619,7 +772,7 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F12" s="37" t="str">
-        <x:v>B00-QUAL-001#REQ-03-02</x:v>
+        <x:v>B00-QUAL-001#REQ-03-02 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -639,10 +792,10 @@
         <x:v>B00-QUAL-001</x:v>
       </x:c>
       <x:c r="F13" s="37" t="str">
-        <x:v>B00-QUAL-001#REQ-03-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-QUAL-001#REQ-03-03 | files/设计资料.pdf#p1-p10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A14" s="35" t="str">
         <x:v>REQ-04-01</x:v>
       </x:c>
@@ -659,10 +812,10 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F14" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-04-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-DESIGN-001#REQ-04-01 | files/设计资料.pdf#p1-p10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A15" s="35" t="str">
         <x:v>REQ-05-01</x:v>
       </x:c>
@@ -679,10 +832,10 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F15" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-05-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-DESIGN-001#REQ-05-01 | files/设计资料.pdf#p1-p10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A16" s="35" t="str">
         <x:v>REQ-05-02</x:v>
       </x:c>
@@ -699,7 +852,7 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F16" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-05-02</x:v>
+        <x:v>B00-DESIGN-001#REQ-05-02 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -719,10 +872,10 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F17" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-06-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-DESIGN-001#REQ-06-01 | files/设计资料.pdf#p1-p10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A18" s="35" t="str">
         <x:v>REQ-06-02</x:v>
       </x:c>
@@ -739,10 +892,10 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F18" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-06-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-DESIGN-001#REQ-06-02 | files/设计资料.pdf#p1-p10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A19" s="35" t="str">
         <x:v>REQ-07-01</x:v>
       </x:c>
@@ -759,10 +912,10 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F19" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-07-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-DESIGN-001#REQ-07-01 | files/设计资料.pdf#p1-p10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A20" s="35" t="str">
         <x:v>REQ-07-02</x:v>
       </x:c>
@@ -779,7 +932,7 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F20" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-07-02</x:v>
+        <x:v>B00-DESIGN-001#REQ-07-02 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -799,7 +952,7 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F21" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-08-01</x:v>
+        <x:v>B00-DESIGN-001#REQ-08-01 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -819,10 +972,10 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F22" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-09-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-DESIGN-001#REQ-09-01 | files/设计资料.pdf#p1-p10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A23" s="35" t="str">
         <x:v>REQ-09-02</x:v>
       </x:c>
@@ -839,10 +992,10 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F23" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-09-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-DESIGN-001#REQ-09-02 | files/设计资料.pdf#p1-p10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A24" s="35" t="str">
         <x:v>REQ-09-03</x:v>
       </x:c>
@@ -859,7 +1012,7 @@
         <x:v>B00-DESIGN-001</x:v>
       </x:c>
       <x:c r="F24" s="37" t="str">
-        <x:v>B00-DESIGN-001#REQ-09-03</x:v>
+        <x:v>B00-DESIGN-001#REQ-09-03 | files/设计资料.pdf#p1-p10</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -922,7 +1075,7 @@
         <x:v>B00-MATERIAL-001#REQ-11-02</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="15" hidden="0" customHeight="1">
+    <x:row r="28" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A28" s="35" t="str">
         <x:v>REQ-12-01</x:v>
       </x:c>
@@ -939,10 +1092,10 @@
         <x:v>B00-MATERIAL-001</x:v>
       </x:c>
       <x:c r="F28" s="37" t="str">
-        <x:v>B00-MATERIAL-001#REQ-12-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-MATERIAL-001#REQ-12-01 | files/材质证书.pdf#p1-p7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A29" s="35" t="str">
         <x:v>REQ-12-02</x:v>
       </x:c>
@@ -959,10 +1112,10 @@
         <x:v>B00-MATERIAL-001</x:v>
       </x:c>
       <x:c r="F29" s="37" t="str">
-        <x:v>B00-MATERIAL-001#REQ-12-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-MATERIAL-001#REQ-12-02 | files/材质证书.pdf#p1-p7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A30" s="35" t="str">
         <x:v>REQ-13-01</x:v>
       </x:c>
@@ -979,10 +1132,10 @@
         <x:v>B00-MATERIAL-001</x:v>
       </x:c>
       <x:c r="F30" s="37" t="str">
-        <x:v>B00-MATERIAL-001#REQ-13-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-MATERIAL-001#REQ-13-01 | files/材质证书.pdf#p1-p7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A31" s="35" t="str">
         <x:v>REQ-13-02</x:v>
       </x:c>
@@ -999,10 +1152,10 @@
         <x:v>B00-MATERIAL-001</x:v>
       </x:c>
       <x:c r="F31" s="37" t="str">
-        <x:v>B00-MATERIAL-001#REQ-13-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-MATERIAL-001#REQ-13-02 | files/材质证书.pdf#p1-p7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A32" s="35" t="str">
         <x:v>REQ-14-01</x:v>
       </x:c>
@@ -1019,10 +1172,10 @@
         <x:v>B00-MATERIAL-001</x:v>
       </x:c>
       <x:c r="F32" s="37" t="str">
-        <x:v>B00-MATERIAL-001#REQ-14-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-MATERIAL-001#REQ-14-01 | files/材质证书.pdf#p1-p7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A33" s="35" t="str">
         <x:v>REQ-14-02</x:v>
       </x:c>
@@ -1039,7 +1192,7 @@
         <x:v>B00-MATERIAL-001</x:v>
       </x:c>
       <x:c r="F33" s="37" t="str">
-        <x:v>B00-MATERIAL-001#REQ-14-02</x:v>
+        <x:v>B00-MATERIAL-001#REQ-14-02 | files/材质证书.pdf#p1-p7</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -1516,10 +1669,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E57" s="36" t="str">
-        <x:v>S01-ACCEPT-001</x:v>
+        <x:v>S01-PHOTO-001</x:v>
       </x:c>
       <x:c r="F57" s="37" t="str">
-        <x:v>S01-ACCEPT-001#REQ-21-03</x:v>
+        <x:v>S01-PHOTO-001#REQ-21-03</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1679,7 +1832,7 @@
         <x:v>B00-WELD-001</x:v>
       </x:c>
       <x:c r="F65" s="37" t="str">
-        <x:v>B00-WELD-001#REQ-24-01</x:v>
+        <x:v>B00-WELD-001#REQ-24-01 | files/资质证书.pdf#p1-p6</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1699,7 +1852,7 @@
         <x:v>B00-WELD-001</x:v>
       </x:c>
       <x:c r="F66" s="37" t="str">
-        <x:v>B00-WELD-001#REQ-24-02</x:v>
+        <x:v>B00-WELD-001#REQ-24-02 | files/资质证书.pdf#p1-p6</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1716,10 +1869,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E67" s="36" t="str">
-        <x:v>B00-WELD-001</x:v>
+        <x:v>B00-QUERY-001</x:v>
       </x:c>
       <x:c r="F67" s="37" t="str">
-        <x:v>B00-WELD-001#REQ-24-03</x:v>
+        <x:v>B00-QUERY-001#REQ-24-03 | files/资质证书.pdf#p1-p6</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1739,7 +1892,7 @@
         <x:v>B00-WELD-001</x:v>
       </x:c>
       <x:c r="F68" s="37" t="str">
-        <x:v>B00-WELD-001#REQ-24-04</x:v>
+        <x:v>B00-WELD-001#REQ-24-04 | files/资质证书.pdf#p1-p6</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1819,7 +1972,7 @@
         <x:v>B00-WELD-001</x:v>
       </x:c>
       <x:c r="F72" s="37" t="str">
-        <x:v>B00-WELD-001#REQ-26-01</x:v>
+        <x:v>B00-WELD-001#REQ-26-01 | files/材质证书.pdf#p1-p7</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1839,7 +1992,7 @@
         <x:v>B00-WELD-001</x:v>
       </x:c>
       <x:c r="F73" s="37" t="str">
-        <x:v>B00-WELD-001#REQ-26-02</x:v>
+        <x:v>B00-WELD-001#REQ-26-02 | files/材质证书.pdf#p1-p7</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1859,7 +2012,7 @@
         <x:v>B00-WELD-001</x:v>
       </x:c>
       <x:c r="F74" s="37" t="str">
-        <x:v>B00-WELD-001#REQ-27-01</x:v>
+        <x:v>B00-WELD-001#REQ-27-01 | files/材质证书.pdf#p1-p7</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1879,7 +2032,7 @@
         <x:v>B00-WELD-001</x:v>
       </x:c>
       <x:c r="F75" s="37" t="str">
-        <x:v>B00-WELD-001#REQ-27-02</x:v>
+        <x:v>B00-WELD-001#REQ-27-02 | files/材质证书.pdf#p1-p7</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1916,13 +2069,13 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E77" s="36" t="str">
-        <x:v>B00-WELD-LEDGER-001</x:v>
+        <x:v>B00-PHOTO-001</x:v>
       </x:c>
       <x:c r="F77" s="37" t="str">
-        <x:v>B00-WELD-LEDGER-001#REQ-28-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-PHOTO-001#REQ-28-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A78" s="35" t="str">
         <x:v>REQ-29-01</x:v>
       </x:c>
@@ -1939,10 +2092,10 @@
         <x:v>B00-WELD-LEDGER-001</x:v>
       </x:c>
       <x:c r="F78" s="37" t="str">
-        <x:v>B00-WELD-LEDGER-001#REQ-29-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-WELD-LEDGER-001#REQ-29-01 | files/资质证书.pdf#p1-p6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A79" s="35" t="str">
         <x:v>REQ-29-02</x:v>
       </x:c>
@@ -1959,10 +2112,10 @@
         <x:v>B00-WELD-LEDGER-001</x:v>
       </x:c>
       <x:c r="F79" s="37" t="str">
-        <x:v>B00-WELD-LEDGER-001#REQ-29-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-WELD-LEDGER-001#REQ-29-02 | files/资质证书.pdf#p1-p6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A80" s="35" t="str">
         <x:v>REQ-29-03</x:v>
       </x:c>
@@ -1979,7 +2132,7 @@
         <x:v>B00-WELD-LEDGER-001</x:v>
       </x:c>
       <x:c r="F80" s="37" t="str">
-        <x:v>B00-WELD-LEDGER-001#REQ-29-03</x:v>
+        <x:v>B00-WELD-LEDGER-001#REQ-29-03 | files/资质证书.pdf#p1-p6</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -2016,10 +2169,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E82" s="36" t="str">
-        <x:v>B00-WELD-LEDGER-001</x:v>
+        <x:v>B00-PHOTO-002</x:v>
       </x:c>
       <x:c r="F82" s="37" t="str">
-        <x:v>B00-WELD-LEDGER-001#REQ-30-02</x:v>
+        <x:v>B00-PHOTO-002#REQ-30-02</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -2262,7 +2415,7 @@
         <x:v>S03-PWHT-001#REQ-34-04</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="15" hidden="0" customHeight="1">
+    <x:row r="95" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A95" s="35" t="str">
         <x:v>REQ-35-01</x:v>
       </x:c>
@@ -2279,10 +2432,10 @@
         <x:v>B00-NDT-001</x:v>
       </x:c>
       <x:c r="F95" s="37" t="str">
-        <x:v>B00-NDT-001#REQ-35-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-NDT-001#REQ-35-01 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A96" s="35" t="str">
         <x:v>REQ-35-02</x:v>
       </x:c>
@@ -2299,7 +2452,7 @@
         <x:v>B00-NDT-001</x:v>
       </x:c>
       <x:c r="F96" s="37" t="str">
-        <x:v>B00-NDT-001#REQ-35-02</x:v>
+        <x:v>B00-NDT-001#REQ-35-02 | Scan/20260623105636.pdf#p1-p5</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -2342,7 +2495,7 @@
         <x:v>B00-NDT-001#REQ-36-02</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="15" hidden="0" customHeight="1">
+    <x:row r="99" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A99" s="35" t="str">
         <x:v>REQ-37-01</x:v>
       </x:c>
@@ -2359,10 +2512,10 @@
         <x:v>B00-NDT-001</x:v>
       </x:c>
       <x:c r="F99" s="37" t="str">
-        <x:v>B00-NDT-001#REQ-37-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-NDT-001#REQ-37-01 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A100" s="35" t="str">
         <x:v>REQ-37-02</x:v>
       </x:c>
@@ -2379,10 +2532,10 @@
         <x:v>B00-NDT-001</x:v>
       </x:c>
       <x:c r="F100" s="37" t="str">
-        <x:v>B00-NDT-001#REQ-37-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-NDT-001#REQ-37-02 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A101" s="35" t="str">
         <x:v>REQ-38-01</x:v>
       </x:c>
@@ -2399,10 +2552,10 @@
         <x:v>B00-NDT-001</x:v>
       </x:c>
       <x:c r="F101" s="37" t="str">
-        <x:v>B00-NDT-001#REQ-38-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-NDT-001#REQ-38-01 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A102" s="35" t="str">
         <x:v>REQ-38-02</x:v>
       </x:c>
@@ -2419,7 +2572,7 @@
         <x:v>B00-NDT-001</x:v>
       </x:c>
       <x:c r="F102" s="37" t="str">
-        <x:v>B00-NDT-001#REQ-38-02</x:v>
+        <x:v>B00-NDT-001#REQ-38-02 | Scan/20260623105636.pdf#p1-p5</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -2462,7 +2615,7 @@
         <x:v>B00-NDT-001#REQ-39-02</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="15" hidden="0" customHeight="1">
+    <x:row r="105" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A105" s="35" t="str">
         <x:v>REQ-40-01</x:v>
       </x:c>
@@ -2479,10 +2632,10 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F105" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-40-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-INSTALL-001#REQ-40-01 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A106" s="35" t="str">
         <x:v>REQ-41-01</x:v>
       </x:c>
@@ -2496,13 +2649,13 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E106" s="36" t="str">
-        <x:v>B00-INSTALL-001</x:v>
+        <x:v>B00-FILM-001</x:v>
       </x:c>
       <x:c r="F106" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-41-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-FILM-001#REQ-41-01 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A107" s="35" t="str">
         <x:v>REQ-41-02</x:v>
       </x:c>
@@ -2519,10 +2672,10 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F107" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-41-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-INSTALL-001#REQ-41-02 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A108" s="35" t="str">
         <x:v>REQ-42-01</x:v>
       </x:c>
@@ -2536,13 +2689,13 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E108" s="36" t="str">
-        <x:v>B00-INSTALL-001</x:v>
+        <x:v>B00-FILM-002</x:v>
       </x:c>
       <x:c r="F108" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-42-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-FILM-002#REQ-42-01 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A109" s="35" t="str">
         <x:v>REQ-42-02</x:v>
       </x:c>
@@ -2559,10 +2712,10 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F109" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-42-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-INSTALL-001#REQ-42-02 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A110" s="35" t="str">
         <x:v>REQ-42-03</x:v>
       </x:c>
@@ -2576,13 +2729,13 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E110" s="36" t="str">
-        <x:v>B00-INSTALL-001</x:v>
+        <x:v>B00-PHOTO-003</x:v>
       </x:c>
       <x:c r="F110" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-42-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-PHOTO-003#REQ-42-03 | Scan/20260623105636.pdf#p1-p5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A111" s="35" t="str">
         <x:v>REQ-43-01</x:v>
       </x:c>
@@ -2599,10 +2752,10 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F111" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-43-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-INSTALL-001#REQ-43-01 | files/材质证书.pdf#p1-p7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A112" s="35" t="str">
         <x:v>REQ-43-02</x:v>
       </x:c>
@@ -2619,10 +2772,10 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F112" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-43-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-INSTALL-001#REQ-43-02 | files/材质证书.pdf#p1-p7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A113" s="35" t="str">
         <x:v>REQ-44-01</x:v>
       </x:c>
@@ -2639,10 +2792,10 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F113" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-44-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-INSTALL-001#REQ-44-01 | files/交工资料.pdf#p1-p24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A114" s="35" t="str">
         <x:v>REQ-44-02</x:v>
       </x:c>
@@ -2656,13 +2809,13 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E114" s="36" t="str">
-        <x:v>B00-INSTALL-001</x:v>
+        <x:v>B00-PHOTO-004</x:v>
       </x:c>
       <x:c r="F114" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-44-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-PHOTO-004#REQ-44-02 | files/交工资料.pdf#p1-p24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A115" s="35" t="str">
         <x:v>REQ-45-01</x:v>
       </x:c>
@@ -2679,10 +2832,10 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F115" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-45-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-INSTALL-001#REQ-45-01 | files/交工资料.pdf#p1-p24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A116" s="35" t="str">
         <x:v>REQ-45-02</x:v>
       </x:c>
@@ -2699,7 +2852,7 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F116" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-45-02</x:v>
+        <x:v>B00-INSTALL-001#REQ-45-02 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2759,7 +2912,7 @@
         <x:v>S04-CP-001</x:v>
       </x:c>
       <x:c r="F119" s="37" t="str">
-        <x:v>S04-CP-001#REQ-47-01</x:v>
+        <x:v>S04-CP-001#REQ-47-01 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2779,7 +2932,7 @@
         <x:v>S04-CP-001</x:v>
       </x:c>
       <x:c r="F120" s="37" t="str">
-        <x:v>S04-CP-001#REQ-47-02</x:v>
+        <x:v>S04-CP-001#REQ-47-02 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2836,10 +2989,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E123" s="36" t="str">
-        <x:v>S04-INSTALL-001</x:v>
+        <x:v>S04-PHOTO-001</x:v>
       </x:c>
       <x:c r="F123" s="37" t="str">
-        <x:v>S04-INSTALL-001#REQ-48-03</x:v>
+        <x:v>S04-PHOTO-001#REQ-48-03</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2896,10 +3049,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E126" s="36" t="str">
-        <x:v>S04-INSTALL-001</x:v>
+        <x:v>S04-PHOTO-002</x:v>
       </x:c>
       <x:c r="F126" s="37" t="str">
-        <x:v>S04-INSTALL-001#REQ-49-03</x:v>
+        <x:v>S04-PHOTO-002#REQ-49-03</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2956,10 +3109,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E129" s="36" t="str">
-        <x:v>S04-INSTALL-001</x:v>
+        <x:v>S04-PHOTO-003</x:v>
       </x:c>
       <x:c r="F129" s="37" t="str">
-        <x:v>S04-INSTALL-001#REQ-50-03</x:v>
+        <x:v>S04-PHOTO-003#REQ-50-03</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -3036,10 +3189,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E133" s="36" t="str">
-        <x:v>S04-INSTALL-001</x:v>
+        <x:v>S04-PHOTO-004</x:v>
       </x:c>
       <x:c r="F133" s="37" t="str">
-        <x:v>S04-INSTALL-001#REQ-51-03</x:v>
+        <x:v>S04-PHOTO-004#REQ-51-03</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -3096,10 +3249,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E136" s="36" t="str">
-        <x:v>S04-INSTALL-001</x:v>
+        <x:v>S04-PHOTO-005</x:v>
       </x:c>
       <x:c r="F136" s="37" t="str">
-        <x:v>S04-INSTALL-001#REQ-52-03</x:v>
+        <x:v>S04-PHOTO-005#REQ-52-03</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -3156,10 +3309,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E139" s="36" t="str">
-        <x:v>S04-INSTALL-001</x:v>
+        <x:v>S04-PHOTO-006</x:v>
       </x:c>
       <x:c r="F139" s="37" t="str">
-        <x:v>S04-INSTALL-001#REQ-53-03</x:v>
+        <x:v>S04-PHOTO-006#REQ-53-03</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -3379,7 +3532,7 @@
         <x:v>B00-TEST-001</x:v>
       </x:c>
       <x:c r="F150" s="37" t="str">
-        <x:v>B00-TEST-001#REQ-59-01</x:v>
+        <x:v>B00-TEST-001#REQ-59-01 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -3399,7 +3552,7 @@
         <x:v>B00-TEST-001</x:v>
       </x:c>
       <x:c r="F151" s="37" t="str">
-        <x:v>B00-TEST-001#REQ-59-02</x:v>
+        <x:v>B00-TEST-001#REQ-59-02 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -3419,7 +3572,7 @@
         <x:v>B00-TEST-001</x:v>
       </x:c>
       <x:c r="F152" s="37" t="str">
-        <x:v>B00-TEST-001#REQ-60-01</x:v>
+        <x:v>B00-TEST-001#REQ-60-01 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -3439,7 +3592,7 @@
         <x:v>B00-TEST-001</x:v>
       </x:c>
       <x:c r="F153" s="37" t="str">
-        <x:v>B00-TEST-001#REQ-60-02</x:v>
+        <x:v>B00-TEST-001#REQ-60-02 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -3459,7 +3612,7 @@
         <x:v>B00-TEST-001</x:v>
       </x:c>
       <x:c r="F154" s="37" t="str">
-        <x:v>B00-TEST-001#REQ-61-01</x:v>
+        <x:v>B00-TEST-001#REQ-61-01 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -3479,7 +3632,7 @@
         <x:v>B00-TEST-001</x:v>
       </x:c>
       <x:c r="F155" s="37" t="str">
-        <x:v>B00-TEST-001#REQ-61-02</x:v>
+        <x:v>B00-TEST-001#REQ-61-02 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -3499,7 +3652,7 @@
         <x:v>B00-TEST-001</x:v>
       </x:c>
       <x:c r="F156" s="37" t="str">
-        <x:v>B00-TEST-001#REQ-62-01</x:v>
+        <x:v>B00-TEST-001#REQ-62-01 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -3519,7 +3672,7 @@
         <x:v>B00-TEST-001</x:v>
       </x:c>
       <x:c r="F157" s="37" t="str">
-        <x:v>B00-TEST-001#REQ-62-02</x:v>
+        <x:v>B00-TEST-001#REQ-62-02 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -3636,10 +3789,10 @@
         <x:v>已提供</x:v>
       </x:c>
       <x:c r="E163" s="36" t="str">
-        <x:v>S06-ALTERNATIVE-001</x:v>
+        <x:v>S06-FILM-001</x:v>
       </x:c>
       <x:c r="F163" s="37" t="str">
-        <x:v>S06-ALTERNATIVE-001#REQ-65-02</x:v>
+        <x:v>S06-FILM-001#REQ-65-02</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -3742,7 +3895,7 @@
         <x:v>S06-FINAL-001#REQ-67-02</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="15" hidden="0" customHeight="1">
+    <x:row r="169" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A169" s="35" t="str">
         <x:v>REQ-68-01</x:v>
       </x:c>
@@ -3759,10 +3912,10 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F169" s="37" t="str">
-        <x:v>B00-INSTALL-001#REQ-68-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" ht="15" hidden="0" customHeight="1">
+        <x:v>B00-INSTALL-001#REQ-68-01 | files/交工资料.pdf#p1-p24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A170" s="38" t="str">
         <x:v>REQ-68-02</x:v>
       </x:c>
@@ -3779,15 +3932,51 @@
         <x:v>B00-INSTALL-001</x:v>
       </x:c>
       <x:c r="F170" s="40" t="str">
-        <x:v>B00-INSTALL-001#REQ-68-02</x:v>
+        <x:v>B00-INSTALL-001#REQ-68-02 | files/交工资料.pdf#p1-p24</x:v>
       </x:c>
     </x:row>
     <x:row r="171"/>
-    <x:row r="172"/>
+    <x:row r="172" ht="15" hidden="0" customHeight="1">
+      <x:c r="A172" s="60" t="str">
+        <x:v>电子签署（测试）｜资料验收测试专用章</x:v>
+      </x:c>
+      <x:c r="B172" s="61"/>
+      <x:c r="C172" s="61"/>
+      <x:c r="D172" s="61"/>
+      <x:c r="E172" s="61"/>
+      <x:c r="F172" s="62"/>
+    </x:row>
+    <x:row r="173" ht="15" hidden="0" customHeight="1">
+      <x:c r="A173" s="63"/>
+      <x:c r="B173" s="64"/>
+      <x:c r="C173" s="64"/>
+      <x:c r="D173" s="64"/>
+      <x:c r="E173" s="64"/>
+      <x:c r="F173" s="65"/>
+    </x:row>
+    <x:row r="174" ht="15" hidden="0" customHeight="1">
+      <x:c r="A174" s="63"/>
+      <x:c r="B174" s="64"/>
+      <x:c r="C174" s="64"/>
+      <x:c r="D174" s="64"/>
+      <x:c r="E174" s="64"/>
+      <x:c r="F174" s="65"/>
+    </x:row>
+    <x:row r="175" ht="15" hidden="0" customHeight="1">
+      <x:c r="A175" s="66"/>
+      <x:c r="B175" s="67"/>
+      <x:c r="C175" s="67"/>
+      <x:c r="D175" s="67"/>
+      <x:c r="E175" s="67"/>
+      <x:c r="F175" s="68"/>
+    </x:row>
+    <x:row r="176"/>
+    <x:row r="177"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A172:C172"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:F170">
     <x:cfRule type="expression" dxfId="0" priority="1">
@@ -3798,5 +3987,6 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5045b2e7157c4747"/>
 </x:worksheet>
 </file>